--- a/VerveStacks_JPN/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_JPN/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77D12D5B-F235-4325-9ACF-CEDA3E7C333D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{38924833-27CD-4A0D-8E14-02A82ED7658F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -911,10 +911,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>RaD,WaP,FaP,SaP,RaP,FaD,SaD,WaD</t>
+    <t>WaD,FaP,SaP,SaD,RaP,WaP,FaD,RaD</t>
   </si>
   <si>
-    <t>FaN,SaN,WaN,RaN,RaP,WaP,FaP,SaP</t>
+    <t>WaP,FaP,SaP,SaN,WaN,RaN,RaP,FaN</t>
   </si>
 </sst>
 </file>
@@ -24570,7 +24570,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79FE9864-CB42-43EE-918C-A400134FBA4F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82186C5E-E13F-4508-9A7C-EA1B3DB3E564}">
   <dimension ref="A9:AN54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24908,7 +24908,7 @@
         <v>151</v>
       </c>
       <c r="AM13">
-        <v>0.28403614521636705</v>
+        <v>0.28403614521636716</v>
       </c>
       <c r="AN13" t="s">
         <v>270</v>
@@ -25258,7 +25258,7 @@
         <v>151</v>
       </c>
       <c r="AM20">
-        <v>0.29725000000000001</v>
+        <v>0.29724999999999996</v>
       </c>
       <c r="AN20" t="s">
         <v>270</v>
@@ -25408,7 +25408,7 @@
         <v>151</v>
       </c>
       <c r="AM23">
-        <v>0.29926666666666674</v>
+        <v>0.29926666666666668</v>
       </c>
       <c r="AN23" t="s">
         <v>270</v>
@@ -25558,7 +25558,7 @@
         <v>151</v>
       </c>
       <c r="AM26">
-        <v>0.29800833333333338</v>
+        <v>0.29800833333333332</v>
       </c>
       <c r="AN26" t="s">
         <v>270</v>
@@ -25608,7 +25608,7 @@
         <v>151</v>
       </c>
       <c r="AM27">
-        <v>0.29666666666666663</v>
+        <v>0.29666666666666669</v>
       </c>
       <c r="AN27" t="s">
         <v>270</v>
@@ -25708,7 +25708,7 @@
         <v>151</v>
       </c>
       <c r="AM29">
-        <v>0.33389166666666664</v>
+        <v>0.3338916666666667</v>
       </c>
       <c r="AN29" t="s">
         <v>270</v>
@@ -25908,7 +25908,7 @@
         <v>151</v>
       </c>
       <c r="AM33">
-        <v>0.29149166666666659</v>
+        <v>0.29149166666666665</v>
       </c>
       <c r="AN33" t="s">
         <v>270</v>
@@ -26158,7 +26158,7 @@
         <v>151</v>
       </c>
       <c r="AM38">
-        <v>0.29490833333333327</v>
+        <v>0.29490833333333333</v>
       </c>
       <c r="AN38" t="s">
         <v>270</v>
@@ -26478,7 +26478,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6180E4AF-7ABD-4CDC-B6B8-E288EA64A378}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A295DE-16C3-4C1B-914C-BDAE7E12C465}">
   <dimension ref="A9:AN538"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26707,7 +26707,7 @@
         <v>271</v>
       </c>
       <c r="AM11">
-        <v>0.23974469689443209</v>
+        <v>0.23974469689443212</v>
       </c>
       <c r="AN11" t="s">
         <v>270</v>
@@ -27128,7 +27128,7 @@
         <v>273</v>
       </c>
       <c r="AM16">
-        <v>0.37560454384911296</v>
+        <v>0.3756045438491129</v>
       </c>
       <c r="AN16" t="s">
         <v>270</v>
@@ -27368,7 +27368,7 @@
         <v>271</v>
       </c>
       <c r="AM19">
-        <v>0.25478850504588313</v>
+        <v>0.25478850504588318</v>
       </c>
       <c r="AN19" t="s">
         <v>270</v>
@@ -27726,7 +27726,7 @@
         <v>273</v>
       </c>
       <c r="AM24">
-        <v>0.27543333333333331</v>
+        <v>0.27543333333333336</v>
       </c>
       <c r="AN24" t="s">
         <v>270</v>
@@ -27785,7 +27785,7 @@
         <v>274</v>
       </c>
       <c r="AM25">
-        <v>0.29716666666666663</v>
+        <v>0.29716666666666669</v>
       </c>
       <c r="AN25" t="s">
         <v>270</v>
@@ -28316,7 +28316,7 @@
         <v>276</v>
       </c>
       <c r="AM34">
-        <v>0.18129999999999999</v>
+        <v>0.18130000000000002</v>
       </c>
       <c r="AN34" t="s">
         <v>270</v>
@@ -28616,7 +28616,7 @@
         <v>273</v>
       </c>
       <c r="AM40">
-        <v>0.35266666666666668</v>
+        <v>0.35266666666666663</v>
       </c>
       <c r="AN40" t="s">
         <v>270</v>
@@ -28816,7 +28816,7 @@
         <v>273</v>
       </c>
       <c r="AM44">
-        <v>0.35719999999999996</v>
+        <v>0.35720000000000002</v>
       </c>
       <c r="AN44" t="s">
         <v>270</v>
@@ -28916,7 +28916,7 @@
         <v>276</v>
       </c>
       <c r="AM46">
-        <v>0.22219999999999998</v>
+        <v>0.22220000000000004</v>
       </c>
       <c r="AN46" t="s">
         <v>270</v>
@@ -29066,7 +29066,7 @@
         <v>274</v>
       </c>
       <c r="AM49">
-        <v>0.35790000000000005</v>
+        <v>0.35789999999999994</v>
       </c>
       <c r="AN49" t="s">
         <v>270</v>
@@ -29116,7 +29116,7 @@
         <v>276</v>
       </c>
       <c r="AM50">
-        <v>0.21673333333333333</v>
+        <v>0.21673333333333336</v>
       </c>
       <c r="AN50" t="s">
         <v>270</v>
@@ -29666,7 +29666,7 @@
         <v>274</v>
       </c>
       <c r="AM61">
-        <v>0.37543333333333334</v>
+        <v>0.37543333333333329</v>
       </c>
       <c r="AN61" t="s">
         <v>270</v>
@@ -29916,7 +29916,7 @@
         <v>276</v>
       </c>
       <c r="AM66">
-        <v>0.22353333333333336</v>
+        <v>0.22353333333333333</v>
       </c>
       <c r="AN66" t="s">
         <v>270</v>
@@ -30466,7 +30466,7 @@
         <v>274</v>
       </c>
       <c r="AM77">
-        <v>0.37416666666666659</v>
+        <v>0.3741666666666667</v>
       </c>
       <c r="AN77" t="s">
         <v>270</v>
@@ -30666,7 +30666,7 @@
         <v>274</v>
       </c>
       <c r="AM81">
-        <v>0.40093333333333331</v>
+        <v>0.40093333333333336</v>
       </c>
       <c r="AN81" t="s">
         <v>270</v>
@@ -30716,7 +30716,7 @@
         <v>276</v>
       </c>
       <c r="AM82">
-        <v>0.24716666666666667</v>
+        <v>0.24716666666666665</v>
       </c>
       <c r="AN82" t="s">
         <v>270</v>
@@ -30766,7 +30766,7 @@
         <v>271</v>
       </c>
       <c r="AM83">
-        <v>0.28130000000000005</v>
+        <v>0.28129999999999999</v>
       </c>
       <c r="AN83" t="s">
         <v>270</v>
@@ -30916,7 +30916,7 @@
         <v>276</v>
       </c>
       <c r="AM86">
-        <v>0.24556666666666668</v>
+        <v>0.24556666666666663</v>
       </c>
       <c r="AN86" t="s">
         <v>270</v>
@@ -31016,7 +31016,7 @@
         <v>273</v>
       </c>
       <c r="AM88">
-        <v>0.38750000000000001</v>
+        <v>0.38749999999999996</v>
       </c>
       <c r="AN88" t="s">
         <v>270</v>
@@ -31566,7 +31566,7 @@
         <v>271</v>
       </c>
       <c r="AM99">
-        <v>0.24106666666666668</v>
+        <v>0.24106666666666665</v>
       </c>
       <c r="AN99" t="s">
         <v>270</v>
@@ -31766,7 +31766,7 @@
         <v>271</v>
       </c>
       <c r="AM103">
-        <v>0.23880000000000001</v>
+        <v>0.23879999999999998</v>
       </c>
       <c r="AN103" t="s">
         <v>270</v>
@@ -31916,7 +31916,7 @@
         <v>276</v>
       </c>
       <c r="AM106">
-        <v>0.20546666666666666</v>
+        <v>0.20546666666666669</v>
       </c>
       <c r="AN106" t="s">
         <v>270</v>
@@ -32416,7 +32416,7 @@
         <v>273</v>
       </c>
       <c r="AM116">
-        <v>0.33629999999999999</v>
+        <v>0.33630000000000004</v>
       </c>
       <c r="AN116" t="s">
         <v>270</v>
@@ -32516,7 +32516,7 @@
         <v>276</v>
       </c>
       <c r="AM118">
-        <v>0.22026666666666669</v>
+        <v>0.22026666666666664</v>
       </c>
       <c r="AN118" t="s">
         <v>270</v>
@@ -32916,7 +32916,7 @@
         <v>276</v>
       </c>
       <c r="AM126">
-        <v>0.21156666666666668</v>
+        <v>0.21156666666666665</v>
       </c>
       <c r="AN126" t="s">
         <v>270</v>
